--- a/Tables/EPS_TableS4_FromR.xlsx
+++ b/Tables/EPS_TableS4_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,10 +367,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>NumDF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DenDF</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>F value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pr(&gt;F)</t>
         </is>
@@ -389,10 +399,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>89.393</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>39.106</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>

--- a/Tables/EPS_TableS4_FromR.xlsx
+++ b/Tables/EPS_TableS4_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,57 +362,153 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sum Sq</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NumDF</t>
+          <t>Std. Error</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DenDF</t>
+          <t>df</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>F value</t>
+          <t>t_value</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Pr(&gt;F)</t>
+          <t>p_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Morphology</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4772.431</t>
+          <t>6.150</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>25.457</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.541</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MorphologyMucoid</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13.210</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.112</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>89.393</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>39.106</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6.253</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>&lt; 0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Random effect: Pairs (variance)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>69.769</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Random effect: Pairs (LRT vs. no random effect)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18.224 (χ²)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
